--- a/InputData/indst/IFSRF/Industrial Feedstock Switching Recipient Fuel.xlsx
+++ b/InputData/indst/IFSRF/Industrial Feedstock Switching Recipient Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IFSRF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\indst\IFSRF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96EB2BC-0030-40BA-9364-0A5C36AD3468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B331AEC1-3FEE-4919-85E8-52CCF2605635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59310" yWindow="1710" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2790" yWindow="1720" windowWidth="13530" windowHeight="10720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -92,11 +92,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -104,8 +104,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -161,7 +168,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -439,15 +446,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -455,37 +463,38 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -493,18 +502,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" customWidth="1"/>
-    <col min="2" max="6" width="16.54296875" style="3" customWidth="1"/>
-    <col min="7" max="8" width="16.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.25" customWidth="1"/>
+    <col min="2" max="6" width="16.5" style="3" customWidth="1"/>
+    <col min="7" max="8" width="16.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="68" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -539,7 +548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -574,7 +583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -609,7 +618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -644,7 +653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -679,7 +688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -714,7 +723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -749,7 +758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -784,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -819,7 +828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -854,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -890,6 +899,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C6524DC-63EE-4FAE-BC4E-92338BEDB678}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E8BC34A-18B1-4745-AFEB-CB117DADE724}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DDB9111-4EBC-4B2D-83B2-8A74DD489D95}"/>
 </file>